--- a/dev/elementary/HTML Ref.xlsx
+++ b/dev/elementary/HTML Ref.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akirk\Documents\GitHub\_FALLBACK\Fall-Back.github.io\dev\elementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3800DC5A-8C67-4082-A4FB-9777F012DD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20505" windowHeight="9450"/>
+    <workbookView xWindow="-46188" yWindow="-4104" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -302,7 +303,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -628,7 +629,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B91"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -788,14 +789,14 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
@@ -1272,7 +1273,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A1:B91">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B91">
     <sortCondition ref="A52"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
